--- a/tests/data/synthetic/fixture.xlsx
+++ b/tests/data/synthetic/fixture.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>   </t>
+          <t xml:space="preserve">   </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
